--- a/documents/JDT/JDT.xlsx
+++ b/documents/JDT/JDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pg66hua\Documents\GitHub\Mostly_Human\documents\JDT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C998EA6-128E-4074-A62B-CDDB0EA0768D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B87C02-8589-4DBA-8236-726DA6D6F6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{E0F9514E-71B1-4D3A-A758-AA454C20BFD4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0F9514E-71B1-4D3A-A758-AA454C20BFD4}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="135">
   <si>
     <t xml:space="preserve">Semaine </t>
   </si>
@@ -435,6 +435,18 @@
   </si>
   <si>
     <t>recherches sur des explication liée à gRPC (Protocol Buffer, Sérialisation, désérialisation )</t>
+  </si>
+  <si>
+    <t>github</t>
+  </si>
+  <si>
+    <t>nettoyage de mon repo github (fichiers générer par vscode)</t>
+  </si>
+  <si>
+    <t>rendu</t>
+  </si>
+  <si>
+    <t>export des fichier, creation de la release github, mail pour le rendu final</t>
   </si>
 </sst>
 </file>
@@ -9941,7 +9953,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B31B073-5394-4F23-9BD2-8AF0BEAA7F84}">
-  <dimension ref="B2:M108"/>
+  <dimension ref="B2:M72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -10067,8 +10079,8 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="40">
-        <f>SUM(L25,L34,L45,L76,L107)</f>
-        <v>0.625</v>
+        <f>SUM(L25,L34,L45,L58,L71)</f>
+        <v>0.90625</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="42">
@@ -10081,7 +10093,7 @@
       <c r="I10" s="44"/>
       <c r="J10" s="48">
         <f>D10-B10</f>
-        <v>0.28125</v>
+        <v>0</v>
       </c>
       <c r="K10" s="44"/>
       <c r="L10" s="10">
@@ -10810,770 +10822,242 @@
       <c r="M57" s="13"/>
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B58" s="2"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="10">
-        <v>0</v>
-      </c>
-      <c r="M58" s="11"/>
+      <c r="B58" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="18">
+        <f>SUM(L52:M57)</f>
+        <v>0.125</v>
+      </c>
+      <c r="M58" s="19"/>
     </row>
     <row r="59" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="12"/>
-      <c r="M59" s="13"/>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B60" s="2"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="10">
-        <v>0</v>
-      </c>
-      <c r="M60" s="11"/>
-    </row>
-    <row r="61" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="4"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="12"/>
-      <c r="M61" s="13"/>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B62" s="2"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="10">
-        <v>0</v>
-      </c>
-      <c r="M62" s="11"/>
-    </row>
-    <row r="63" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="4"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="13"/>
-    </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B64" s="2"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="10">
-        <v>0</v>
-      </c>
-      <c r="M64" s="11"/>
-    </row>
-    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="4"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="13"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B66" s="2"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="10">
-        <v>0</v>
-      </c>
-      <c r="M66" s="11"/>
-    </row>
-    <row r="67" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="4"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="13"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B68" s="2"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="10">
-        <v>0</v>
-      </c>
-      <c r="M68" s="11"/>
-    </row>
-    <row r="69" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="4"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="13"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B70" s="2"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="10">
-        <v>0</v>
-      </c>
-      <c r="M70" s="11"/>
-    </row>
-    <row r="71" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="4"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="13"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B72" s="2"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="10">
-        <v>0</v>
-      </c>
-      <c r="M72" s="11"/>
-    </row>
-    <row r="73" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="4"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="13"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B74" s="2"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="10">
-        <v>0</v>
-      </c>
-      <c r="M74" s="11"/>
-    </row>
-    <row r="75" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="4"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="13"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B76" s="14" t="s">
+      <c r="B59" s="16"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="21"/>
+    </row>
+    <row r="60" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="23"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="26"/>
+    </row>
+    <row r="62" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="24"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="27"/>
+    </row>
+    <row r="63" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="29"/>
+      <c r="D63" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="K63" s="29"/>
+      <c r="L63" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="M63" s="29"/>
+    </row>
+    <row r="64" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="30"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="31"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="10">
+        <v>0.23263888888888887</v>
+      </c>
+      <c r="M65" s="11"/>
+    </row>
+    <row r="66" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="4"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="13"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="10">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="M67" s="11"/>
+    </row>
+    <row r="68" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="4"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="12"/>
+      <c r="M68" s="13"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="10">
+        <v>3.8194444444444441E-2</v>
+      </c>
+      <c r="M69" s="11"/>
+    </row>
+    <row r="70" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="4"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="13"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B71" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
-      <c r="L76" s="18">
-        <f>SUM(L52:M75)</f>
-        <v>0.125</v>
-      </c>
-      <c r="M76" s="19"/>
-    </row>
-    <row r="77" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="16"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="20"/>
-      <c r="M77" s="21"/>
-    </row>
-    <row r="78" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B79" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="23"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="26"/>
-    </row>
-    <row r="80" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="24"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-      <c r="J80" s="25"/>
-      <c r="K80" s="25"/>
-      <c r="L80" s="25"/>
-      <c r="M80" s="27"/>
-    </row>
-    <row r="81" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="29"/>
-      <c r="D81" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E81" s="32"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="29"/>
-      <c r="J81" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="K81" s="29"/>
-      <c r="L81" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="M81" s="29"/>
-    </row>
-    <row r="82" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="30"/>
-      <c r="C82" s="31"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="33"/>
-      <c r="F82" s="33"/>
-      <c r="G82" s="33"/>
-      <c r="H82" s="33"/>
-      <c r="I82" s="31"/>
-      <c r="J82" s="30"/>
-      <c r="K82" s="31"/>
-      <c r="L82" s="30"/>
-      <c r="M82" s="31"/>
-    </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B83" s="2"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="10">
-        <v>0</v>
-      </c>
-      <c r="M83" s="11"/>
-    </row>
-    <row r="84" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="4"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="12"/>
-      <c r="M84" s="13"/>
-    </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B85" s="2"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="10">
-        <v>0</v>
-      </c>
-      <c r="M85" s="11"/>
-    </row>
-    <row r="86" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="4"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="5"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="5"/>
-      <c r="L86" s="12"/>
-      <c r="M86" s="13"/>
-    </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B87" s="2"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="10">
-        <v>0</v>
-      </c>
-      <c r="M87" s="11"/>
-    </row>
-    <row r="88" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="4"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="5"/>
-      <c r="L88" s="12"/>
-      <c r="M88" s="13"/>
-    </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B89" s="2"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="10">
-        <v>0</v>
-      </c>
-      <c r="M89" s="11"/>
-    </row>
-    <row r="90" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="4"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="12"/>
-      <c r="M90" s="13"/>
-    </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B91" s="2"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="10">
-        <v>0</v>
-      </c>
-      <c r="M91" s="11"/>
-    </row>
-    <row r="92" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="4"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="12"/>
-      <c r="M92" s="13"/>
-    </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B93" s="2"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="10">
-        <v>0</v>
-      </c>
-      <c r="M93" s="11"/>
-    </row>
-    <row r="94" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="4"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="12"/>
-      <c r="M94" s="13"/>
-    </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B95" s="2"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="10">
-        <v>0</v>
-      </c>
-      <c r="M95" s="11"/>
-    </row>
-    <row r="96" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="4"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="12"/>
-      <c r="M96" s="13"/>
-    </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B97" s="2"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="10">
-        <v>0</v>
-      </c>
-      <c r="M97" s="11"/>
-    </row>
-    <row r="98" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="4"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="12"/>
-      <c r="M98" s="13"/>
-    </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B99" s="2"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="10">
-        <v>0</v>
-      </c>
-      <c r="M99" s="11"/>
-    </row>
-    <row r="100" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="4"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="12"/>
-      <c r="M100" s="13"/>
-    </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B101" s="2"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="10">
-        <v>0</v>
-      </c>
-      <c r="M101" s="11"/>
-    </row>
-    <row r="102" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="4"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="9"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="5"/>
-      <c r="L102" s="12"/>
-      <c r="M102" s="13"/>
-    </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B103" s="2"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="10">
-        <v>0</v>
-      </c>
-      <c r="M103" s="11"/>
-    </row>
-    <row r="104" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="4"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="12"/>
-      <c r="M104" s="13"/>
-    </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B105" s="2"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="3"/>
-      <c r="L105" s="10">
-        <v>0</v>
-      </c>
-      <c r="M105" s="11"/>
-    </row>
-    <row r="106" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="4"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="12"/>
-      <c r="M106" s="13"/>
-    </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B107" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="15"/>
-      <c r="D107" s="15"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15"/>
-      <c r="H107" s="15"/>
-      <c r="I107" s="15"/>
-      <c r="J107" s="15"/>
-      <c r="K107" s="15"/>
-      <c r="L107" s="18">
-        <f>SUM(L83:M106)</f>
-        <v>0</v>
-      </c>
-      <c r="M107" s="19"/>
-    </row>
-    <row r="108" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="16"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="17"/>
-      <c r="E108" s="17"/>
-      <c r="F108" s="17"/>
-      <c r="G108" s="17"/>
-      <c r="H108" s="17"/>
-      <c r="I108" s="17"/>
-      <c r="J108" s="17"/>
-      <c r="K108" s="17"/>
-      <c r="L108" s="20"/>
-      <c r="M108" s="21"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="18">
+        <f>SUM(L65:M70)</f>
+        <v>0.28124999999999994</v>
+      </c>
+      <c r="M71" s="19"/>
+    </row>
+    <row r="72" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="16"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
+      <c r="L72" s="20"/>
+      <c r="M72" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="187">
+  <mergeCells count="115">
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:M4"/>
     <mergeCell ref="B6:K7"/>
@@ -11657,10 +11141,6 @@
     <mergeCell ref="D56:I57"/>
     <mergeCell ref="J56:K57"/>
     <mergeCell ref="L56:M57"/>
-    <mergeCell ref="B58:C59"/>
-    <mergeCell ref="D58:I59"/>
-    <mergeCell ref="J58:K59"/>
-    <mergeCell ref="L58:M59"/>
     <mergeCell ref="B52:C53"/>
     <mergeCell ref="D52:I53"/>
     <mergeCell ref="J52:K53"/>
@@ -11669,98 +11149,30 @@
     <mergeCell ref="D54:I55"/>
     <mergeCell ref="J54:K55"/>
     <mergeCell ref="L54:M55"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="D64:I65"/>
-    <mergeCell ref="J64:K65"/>
-    <mergeCell ref="L64:M65"/>
-    <mergeCell ref="B66:C67"/>
-    <mergeCell ref="D66:I67"/>
-    <mergeCell ref="J66:K67"/>
-    <mergeCell ref="L66:M67"/>
-    <mergeCell ref="B60:C61"/>
-    <mergeCell ref="D60:I61"/>
-    <mergeCell ref="J60:K61"/>
-    <mergeCell ref="L60:M61"/>
-    <mergeCell ref="B62:C63"/>
-    <mergeCell ref="D62:I63"/>
-    <mergeCell ref="J62:K63"/>
-    <mergeCell ref="L62:M63"/>
-    <mergeCell ref="B72:C73"/>
-    <mergeCell ref="D72:I73"/>
-    <mergeCell ref="J72:K73"/>
-    <mergeCell ref="L72:M73"/>
-    <mergeCell ref="B74:C75"/>
-    <mergeCell ref="D74:I75"/>
-    <mergeCell ref="J74:K75"/>
-    <mergeCell ref="L74:M75"/>
-    <mergeCell ref="B68:C69"/>
-    <mergeCell ref="D68:I69"/>
-    <mergeCell ref="J68:K69"/>
-    <mergeCell ref="L68:M69"/>
-    <mergeCell ref="B70:C71"/>
-    <mergeCell ref="D70:I71"/>
-    <mergeCell ref="J70:K71"/>
-    <mergeCell ref="L70:M71"/>
-    <mergeCell ref="B83:C84"/>
-    <mergeCell ref="D83:I84"/>
-    <mergeCell ref="J83:K84"/>
-    <mergeCell ref="L83:M84"/>
-    <mergeCell ref="B85:C86"/>
-    <mergeCell ref="D85:I86"/>
-    <mergeCell ref="J85:K86"/>
-    <mergeCell ref="L85:M86"/>
-    <mergeCell ref="B76:C77"/>
-    <mergeCell ref="D76:K77"/>
-    <mergeCell ref="L76:M77"/>
-    <mergeCell ref="B79:K80"/>
-    <mergeCell ref="L79:M80"/>
-    <mergeCell ref="B81:C82"/>
-    <mergeCell ref="D81:I82"/>
-    <mergeCell ref="J81:K82"/>
-    <mergeCell ref="L81:M82"/>
-    <mergeCell ref="B91:C92"/>
-    <mergeCell ref="D91:I92"/>
-    <mergeCell ref="J91:K92"/>
-    <mergeCell ref="L91:M92"/>
-    <mergeCell ref="B93:C94"/>
-    <mergeCell ref="D93:I94"/>
-    <mergeCell ref="J93:K94"/>
-    <mergeCell ref="L93:M94"/>
-    <mergeCell ref="B87:C88"/>
-    <mergeCell ref="D87:I88"/>
-    <mergeCell ref="J87:K88"/>
-    <mergeCell ref="L87:M88"/>
-    <mergeCell ref="B89:C90"/>
-    <mergeCell ref="D89:I90"/>
-    <mergeCell ref="J89:K90"/>
-    <mergeCell ref="L89:M90"/>
-    <mergeCell ref="B99:C100"/>
-    <mergeCell ref="D99:I100"/>
-    <mergeCell ref="J99:K100"/>
-    <mergeCell ref="L99:M100"/>
-    <mergeCell ref="B101:C102"/>
-    <mergeCell ref="D101:I102"/>
-    <mergeCell ref="J101:K102"/>
-    <mergeCell ref="L101:M102"/>
-    <mergeCell ref="B95:C96"/>
-    <mergeCell ref="D95:I96"/>
-    <mergeCell ref="J95:K96"/>
-    <mergeCell ref="L95:M96"/>
-    <mergeCell ref="B97:C98"/>
-    <mergeCell ref="D97:I98"/>
-    <mergeCell ref="J97:K98"/>
-    <mergeCell ref="L97:M98"/>
-    <mergeCell ref="B107:C108"/>
-    <mergeCell ref="D107:K108"/>
-    <mergeCell ref="L107:M108"/>
-    <mergeCell ref="B103:C104"/>
-    <mergeCell ref="D103:I104"/>
-    <mergeCell ref="J103:K104"/>
-    <mergeCell ref="L103:M104"/>
-    <mergeCell ref="B105:C106"/>
-    <mergeCell ref="D105:I106"/>
-    <mergeCell ref="J105:K106"/>
-    <mergeCell ref="L105:M106"/>
+    <mergeCell ref="B58:C59"/>
+    <mergeCell ref="D58:K59"/>
+    <mergeCell ref="L58:M59"/>
+    <mergeCell ref="B61:K62"/>
+    <mergeCell ref="L61:M62"/>
+    <mergeCell ref="B63:C64"/>
+    <mergeCell ref="D63:I64"/>
+    <mergeCell ref="J63:K64"/>
+    <mergeCell ref="L63:M64"/>
+    <mergeCell ref="B71:C72"/>
+    <mergeCell ref="D71:K72"/>
+    <mergeCell ref="L71:M72"/>
+    <mergeCell ref="B69:C70"/>
+    <mergeCell ref="D69:I70"/>
+    <mergeCell ref="J69:K70"/>
+    <mergeCell ref="L69:M70"/>
+    <mergeCell ref="B65:C66"/>
+    <mergeCell ref="D65:I66"/>
+    <mergeCell ref="J65:K66"/>
+    <mergeCell ref="L65:M66"/>
+    <mergeCell ref="B67:C68"/>
+    <mergeCell ref="D67:I68"/>
+    <mergeCell ref="J67:K68"/>
+    <mergeCell ref="L67:M68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
